--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>Patient.typeId.nullFlavor</t>
@@ -1498,7 +1494,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1506,10 +1502,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1607,39 +1603,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1690,7 +1686,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1710,39 +1706,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1793,7 +1789,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1813,17 +1809,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1841,11 +1837,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1854,49 +1850,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1916,17 +1912,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1944,11 +1940,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1999,7 +1995,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2019,10 +2015,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2049,7 +2045,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2100,7 +2096,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2120,10 +2116,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2157,7 +2153,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2179,7 +2175,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2197,7 +2193,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2217,10 +2213,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2254,7 +2250,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2276,7 +2272,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2294,7 +2290,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2314,10 +2310,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2393,7 +2389,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2413,10 +2409,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2439,10 +2435,10 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2494,7 +2490,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2514,10 +2510,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2615,17 +2611,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2678,25 +2674,25 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2716,10 +2712,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2742,11 +2738,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2797,7 +2793,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2809,7 +2805,7 @@
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2817,10 +2813,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2843,7 +2839,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2896,7 +2892,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2916,10 +2912,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2942,7 +2938,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2995,7 +2991,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3015,10 +3011,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3041,7 +3037,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -3094,7 +3090,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3114,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3140,7 +3136,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -3193,7 +3189,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3213,10 +3209,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3239,7 +3235,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3292,7 +3288,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3312,10 +3308,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3338,14 +3334,14 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3395,7 +3391,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3415,17 +3411,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3443,11 +3439,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3498,7 +3494,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3518,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3544,11 +3540,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3599,7 +3595,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3619,10 +3615,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3645,10 +3641,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -3680,7 +3676,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3698,7 +3694,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3718,10 +3714,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3744,10 +3740,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -3799,7 +3795,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3819,10 +3815,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3845,10 +3841,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3900,7 +3896,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3920,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3946,10 +3942,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4001,7 +3997,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4021,10 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4047,10 +4043,10 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -4102,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4122,10 +4118,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4148,10 +4144,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4203,7 +4199,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4223,10 +4219,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4249,7 +4245,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -4278,11 +4274,11 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4300,7 +4296,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4320,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4346,7 +4342,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -4375,11 +4371,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4397,7 +4393,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4417,10 +4413,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4443,7 +4439,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -4472,11 +4468,11 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4494,7 +4490,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4514,10 +4510,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4540,7 +4536,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4569,29 +4565,29 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4611,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4637,7 +4633,7 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -4666,11 +4662,11 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -4688,7 +4684,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4708,10 +4704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4734,7 +4730,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -4763,29 +4759,29 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4805,10 +4801,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4831,10 +4827,10 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -4886,7 +4882,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -4906,10 +4902,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4932,10 +4928,10 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -4987,7 +4983,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5007,10 +5003,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5033,7 +5029,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5086,7 +5082,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>patient</t>
+    <t>CDA - patient</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -943,42 +943,42 @@
   <dimension ref="A1:AK41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.07421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.07421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="31.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="31.78515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="104.4296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.23046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="89.53125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.05859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
